--- a/public/raw-files/PM SALES DATA- March 9-10, 2026.xlsx
+++ b/public/raw-files/PM SALES DATA- March 9-10, 2026.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Github\HotelV2\public\raw-files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CD2AA424AA4B0C96DF91FB37733F9CC2373AF466" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="SALES DATA" sheetId="1" r:id="rId4"/>
+    <sheet name="SALES DATA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'SALES DATA'!$B$2:$P$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SALES DATA'!$B$2:$P$165</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/yanoMHJG+VTyTOQuPhSJtohZG+lHHjJWtbpbSwHokQ="/>
@@ -1304,41 +1314,49 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF111827"/>
       <name val="Quattrocento Sans"/>
     </font>
-    <font/>
     <font>
-      <sz val="10.0"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1346,7 +1364,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1362,12 +1380,19 @@
     </fill>
   </fills>
   <borders count="6">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1382,6 +1407,7 @@
       <bottom style="medium">
         <color rgb="FFD1D5DB"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1393,6 +1419,8 @@
       <top style="medium">
         <color rgb="FFD1D5DB"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1401,9 +1429,11 @@
       <right style="medium">
         <color rgb="FFD1D5DB"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FFD1D5DB"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1412,68 +1442,74 @@
       <right style="medium">
         <color rgb="FFD1D5DB"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1663,33 +1699,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.29"/>
-    <col customWidth="1" min="2" max="2" width="7.14"/>
-    <col customWidth="1" min="3" max="3" width="16.71"/>
-    <col customWidth="1" min="4" max="4" width="20.86"/>
-    <col customWidth="1" min="5" max="5" width="24.43"/>
-    <col customWidth="1" min="6" max="6" width="23.86"/>
-    <col customWidth="1" min="7" max="7" width="10.14"/>
-    <col customWidth="1" min="8" max="9" width="14.86"/>
-    <col customWidth="1" min="10" max="12" width="15.43"/>
-    <col customWidth="1" min="13" max="13" width="13.14"/>
-    <col customWidth="1" min="14" max="14" width="16.86"/>
-    <col customWidth="1" min="15" max="15" width="14.14"/>
-    <col customWidth="1" min="16" max="16" width="16.0"/>
-    <col customWidth="1" min="17" max="26" width="8.71"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="23.88671875" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="8" max="9" width="14.88671875" customWidth="1"/>
+    <col min="10" max="12" width="15.44140625" customWidth="1"/>
+    <col min="13" max="13" width="13.109375" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,12 +1776,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="29.25" customHeight="1">
+    <row r="2" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>16</v>
@@ -1799,12 +1836,12 @@
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
     </row>
-    <row r="3" ht="29.25" customHeight="1">
+    <row r="3" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>16</v>
@@ -1859,9 +1896,9 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
     </row>
-    <row r="4" ht="29.25" hidden="1" customHeight="1">
+    <row r="4" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>30</v>
@@ -1909,9 +1946,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" ht="29.25" hidden="1" customHeight="1">
+    <row r="5" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>36</v>
@@ -1959,9 +1996,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" ht="29.25" customHeight="1">
+    <row r="6" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>41</v>
@@ -2009,11 +2046,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="29.25" customHeight="1">
+    <row r="7" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
-        <v>12.0</v>
-      </c>
-      <c r="B7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -2059,11 +2096,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="29.25" customHeight="1">
+    <row r="8" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
-        <v>13.0</v>
-      </c>
-      <c r="B8" s="11"/>
+        <v>13</v>
+      </c>
+      <c r="B8" s="15"/>
       <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
@@ -2107,9 +2144,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" ht="29.25" customHeight="1">
+    <row r="9" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>54</v>
@@ -2157,9 +2194,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" ht="29.25" hidden="1" customHeight="1">
+    <row r="10" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>58</v>
@@ -2207,11 +2244,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="29.25" hidden="1" customHeight="1">
+    <row r="11" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="B11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>62</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -2257,11 +2294,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" ht="29.25" hidden="1" customHeight="1">
+    <row r="12" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
-        <v>17.0</v>
-      </c>
-      <c r="B12" s="11"/>
+        <v>17</v>
+      </c>
+      <c r="B12" s="15"/>
       <c r="C12" s="9" t="s">
         <v>31</v>
       </c>
@@ -2305,11 +2342,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" ht="29.25" customHeight="1">
+    <row r="13" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
-        <v>18.0</v>
-      </c>
-      <c r="B13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2355,11 +2392,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" ht="29.25" hidden="1" customHeight="1">
+    <row r="14" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
-        <v>19.0</v>
-      </c>
-      <c r="B14" s="11"/>
+        <v>19</v>
+      </c>
+      <c r="B14" s="15"/>
       <c r="C14" s="9" t="s">
         <v>31</v>
       </c>
@@ -2403,10 +2440,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" ht="29.25" hidden="1" customHeight="1">
+    <row r="15" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>16</v>
@@ -2451,12 +2488,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="29.25" hidden="1" customHeight="1">
+    <row r="16" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
-        <v>20.0</v>
-      </c>
-      <c r="B16" s="10">
-        <v>15.0</v>
+        <v>20</v>
+      </c>
+      <c r="B16" s="14">
+        <v>15</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>77</v>
@@ -2501,11 +2538,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" ht="29.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
-        <v>21.0</v>
-      </c>
-      <c r="B17" s="11"/>
+        <v>21</v>
+      </c>
+      <c r="B17" s="15"/>
       <c r="C17" s="9" t="s">
         <v>77</v>
       </c>
@@ -2549,12 +2586,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" ht="29.25" customHeight="1">
+    <row r="18" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B18" s="8">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -2599,12 +2636,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" ht="29.25" hidden="1" customHeight="1">
+    <row r="19" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B19" s="8">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>16</v>
@@ -2649,12 +2686,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" ht="29.25" hidden="1" customHeight="1">
+    <row r="20" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B20" s="8">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>16</v>
@@ -2699,12 +2736,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="29.25" hidden="1" customHeight="1">
+    <row r="21" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
-        <v>25.0</v>
-      </c>
-      <c r="B21" s="10">
-        <v>19.0</v>
+        <v>25</v>
+      </c>
+      <c r="B21" s="14">
+        <v>19</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>77</v>
@@ -2749,11 +2786,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" ht="29.25" hidden="1" customHeight="1">
+    <row r="22" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
-        <v>26.0</v>
-      </c>
-      <c r="B22" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="B22" s="15"/>
       <c r="C22" s="9" t="s">
         <v>77</v>
       </c>
@@ -2797,12 +2834,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" ht="29.25" hidden="1" customHeight="1">
+    <row r="23" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
-        <v>27.0</v>
-      </c>
-      <c r="B23" s="10">
-        <v>20.0</v>
+        <v>27</v>
+      </c>
+      <c r="B23" s="14">
+        <v>20</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>16</v>
@@ -2847,11 +2884,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" ht="29.25" hidden="1" customHeight="1">
+    <row r="24" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
-        <v>28.0</v>
-      </c>
-      <c r="B24" s="12"/>
+        <v>28</v>
+      </c>
+      <c r="B24" s="16"/>
       <c r="C24" s="9" t="s">
         <v>16</v>
       </c>
@@ -2895,11 +2932,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" ht="29.25" customHeight="1">
+    <row r="25" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
-        <v>29.0</v>
-      </c>
-      <c r="B25" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="B25" s="16"/>
       <c r="C25" s="5" t="s">
         <v>16</v>
       </c>
@@ -2943,11 +2980,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" ht="29.25" customHeight="1">
+    <row r="26" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="B26" s="11"/>
+        <v>30</v>
+      </c>
+      <c r="B26" s="15"/>
       <c r="C26" s="5" t="s">
         <v>16</v>
       </c>
@@ -2991,12 +3028,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" ht="29.25" customHeight="1">
+    <row r="27" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B27" s="8">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -3041,12 +3078,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" ht="29.25" customHeight="1">
+    <row r="28" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
-        <v>32.0</v>
-      </c>
-      <c r="B28" s="10">
-        <v>24.0</v>
+        <v>32</v>
+      </c>
+      <c r="B28" s="14">
+        <v>24</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>16</v>
@@ -3091,11 +3128,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" ht="29.25" customHeight="1">
+    <row r="29" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
-        <v>33.0</v>
-      </c>
-      <c r="B29" s="11"/>
+        <v>33</v>
+      </c>
+      <c r="B29" s="15"/>
       <c r="C29" s="5" t="s">
         <v>16</v>
       </c>
@@ -3139,12 +3176,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" ht="29.25" hidden="1" customHeight="1">
+    <row r="30" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
-        <v>34.0</v>
-      </c>
-      <c r="B30" s="10">
-        <v>27.0</v>
+        <v>34</v>
+      </c>
+      <c r="B30" s="14">
+        <v>27</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>16</v>
@@ -3189,11 +3226,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="29.25" hidden="1" customHeight="1">
+    <row r="31" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
-        <v>35.0</v>
-      </c>
-      <c r="B31" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="B31" s="15"/>
       <c r="C31" s="9" t="s">
         <v>16</v>
       </c>
@@ -3237,12 +3274,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" ht="29.25" customHeight="1">
+    <row r="32" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B32" s="8">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
@@ -3287,12 +3324,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" ht="29.25" hidden="1" customHeight="1">
+    <row r="33" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B33" s="8">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>16</v>
@@ -3337,12 +3374,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" ht="29.25" customHeight="1">
+    <row r="34" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B34" s="8">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>16</v>
@@ -3387,12 +3424,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" ht="29.25" hidden="1" customHeight="1">
+    <row r="35" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
-        <v>39.0</v>
-      </c>
-      <c r="B35" s="10">
-        <v>62.0</v>
+        <v>39</v>
+      </c>
+      <c r="B35" s="14">
+        <v>62</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>16</v>
@@ -3437,11 +3474,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" ht="29.25" hidden="1" customHeight="1">
+    <row r="36" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
-        <v>40.0</v>
-      </c>
-      <c r="B36" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="B36" s="16"/>
       <c r="C36" s="9" t="s">
         <v>16</v>
       </c>
@@ -3485,11 +3522,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" ht="29.25" hidden="1" customHeight="1">
+    <row r="37" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
-        <v>41.0</v>
-      </c>
-      <c r="B37" s="12"/>
+        <v>41</v>
+      </c>
+      <c r="B37" s="16"/>
       <c r="C37" s="9" t="s">
         <v>16</v>
       </c>
@@ -3533,11 +3570,11 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="29.25" hidden="1" customHeight="1">
+    <row r="38" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
-        <v>42.0</v>
-      </c>
-      <c r="B38" s="11"/>
+        <v>42</v>
+      </c>
+      <c r="B38" s="15"/>
       <c r="C38" s="9" t="s">
         <v>16</v>
       </c>
@@ -3581,10 +3618,10 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" ht="29.25" customHeight="1">
+    <row r="39" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="8">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>16</v>
@@ -3629,12 +3666,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" ht="29.25" hidden="1" customHeight="1">
+    <row r="40" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B40" s="8">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>16</v>
@@ -3679,12 +3716,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" ht="29.25" customHeight="1">
+    <row r="41" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B41" s="8">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>16</v>
@@ -3729,12 +3766,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" ht="29.25" customHeight="1">
+    <row r="42" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B42" s="8">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>16</v>
@@ -3779,12 +3816,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" ht="29.25" hidden="1" customHeight="1">
+    <row r="43" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
-        <v>46.0</v>
-      </c>
-      <c r="B43" s="10">
-        <v>70.0</v>
+        <v>46</v>
+      </c>
+      <c r="B43" s="14">
+        <v>70</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>77</v>
@@ -3829,11 +3866,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" ht="29.25" hidden="1" customHeight="1">
+    <row r="44" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
-        <v>47.0</v>
-      </c>
-      <c r="B44" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="B44" s="15"/>
       <c r="C44" s="9" t="s">
         <v>77</v>
       </c>
@@ -3877,12 +3914,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" ht="29.25" customHeight="1">
+    <row r="45" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B45" s="8">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>16</v>
@@ -3927,12 +3964,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" ht="29.25" hidden="1" customHeight="1">
+    <row r="46" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B46" s="8">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>16</v>
@@ -3977,12 +4014,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" ht="29.25" customHeight="1">
+    <row r="47" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B47" s="8">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>16</v>
@@ -4027,12 +4064,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" ht="29.25" hidden="1" customHeight="1">
+    <row r="48" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
-        <v>51.0</v>
-      </c>
-      <c r="B48" s="10">
-        <v>75.0</v>
+        <v>51</v>
+      </c>
+      <c r="B48" s="14">
+        <v>75</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>16</v>
@@ -4077,11 +4114,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="49" ht="29.25" hidden="1" customHeight="1">
+    <row r="49" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
-        <v>52.0</v>
-      </c>
-      <c r="B49" s="11"/>
+        <v>52</v>
+      </c>
+      <c r="B49" s="15"/>
       <c r="C49" s="9" t="s">
         <v>16</v>
       </c>
@@ -4125,12 +4162,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="50" ht="29.25" customHeight="1">
+    <row r="50" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B50" s="8">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>16</v>
@@ -4175,12 +4212,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" ht="29.25" customHeight="1">
+    <row r="51" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="B51" s="8">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>16</v>
@@ -4225,12 +4262,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" ht="29.25" customHeight="1">
+    <row r="52" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="B52" s="8">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>16</v>
@@ -4275,12 +4312,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" ht="29.25" customHeight="1">
+    <row r="53" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="B53" s="8">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>16</v>
@@ -4325,12 +4362,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" ht="29.25" hidden="1" customHeight="1">
+    <row r="54" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B54" s="8">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>16</v>
@@ -4375,12 +4412,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" ht="29.25" customHeight="1">
+    <row r="55" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B55" s="8">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>16</v>
@@ -4425,12 +4462,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" ht="29.25" customHeight="1">
+    <row r="56" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="B56" s="8">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>16</v>
@@ -4475,12 +4512,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" ht="29.25" customHeight="1">
+    <row r="57" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="B57" s="8">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>16</v>
@@ -4525,12 +4562,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" ht="29.25" hidden="1" customHeight="1">
+    <row r="58" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
-        <v>61.0</v>
-      </c>
-      <c r="B58" s="10">
-        <v>92.0</v>
+        <v>61</v>
+      </c>
+      <c r="B58" s="14">
+        <v>92</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>16</v>
@@ -4575,11 +4612,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" ht="29.25" hidden="1" customHeight="1">
+    <row r="59" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
-        <v>62.0</v>
-      </c>
-      <c r="B59" s="11"/>
+        <v>62</v>
+      </c>
+      <c r="B59" s="15"/>
       <c r="C59" s="9" t="s">
         <v>16</v>
       </c>
@@ -4623,12 +4660,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" ht="29.25" customHeight="1">
+    <row r="60" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B60" s="8">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>16</v>
@@ -4673,12 +4710,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" ht="29.25" customHeight="1">
+    <row r="61" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
-        <v>64.0</v>
-      </c>
-      <c r="B61" s="10">
-        <v>99.0</v>
+        <v>64</v>
+      </c>
+      <c r="B61" s="14">
+        <v>99</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>16</v>
@@ -4723,9 +4760,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" ht="29.25" customHeight="1">
+    <row r="62" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
-      <c r="B62" s="11"/>
+      <c r="B62" s="15"/>
       <c r="C62" s="5" t="s">
         <v>16</v>
       </c>
@@ -4769,12 +4806,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" ht="29.25" hidden="1" customHeight="1">
+    <row r="63" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B63" s="8">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>16</v>
@@ -4819,12 +4856,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" ht="29.25" hidden="1" customHeight="1">
+    <row r="64" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B64" s="8">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>16</v>
@@ -4869,12 +4906,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" ht="29.25" hidden="1" customHeight="1">
+    <row r="65" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
-        <v>67.0</v>
-      </c>
-      <c r="B65" s="10">
-        <v>127.0</v>
+        <v>67</v>
+      </c>
+      <c r="B65" s="14">
+        <v>127</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>16</v>
@@ -4919,11 +4956,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" ht="29.25" hidden="1" customHeight="1">
+    <row r="66" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
-        <v>68.0</v>
-      </c>
-      <c r="B66" s="11"/>
+        <v>68</v>
+      </c>
+      <c r="B66" s="15"/>
       <c r="C66" s="9" t="s">
         <v>16</v>
       </c>
@@ -4967,12 +5004,12 @@
         <v>197</v>
       </c>
     </row>
-    <row r="67" ht="29.25" customHeight="1">
+    <row r="67" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="B67" s="8">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>16</v>
@@ -5017,12 +5054,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" ht="29.25" hidden="1" customHeight="1">
+    <row r="68" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="B68" s="8">
-        <v>132.0</v>
+        <v>132</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>16</v>
@@ -5067,12 +5104,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" ht="29.25" hidden="1" customHeight="1">
+    <row r="69" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
-        <v>71.0</v>
-      </c>
-      <c r="B69" s="10">
-        <v>136.0</v>
+        <v>71</v>
+      </c>
+      <c r="B69" s="14">
+        <v>136</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>16</v>
@@ -5117,11 +5154,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" ht="29.25" hidden="1" customHeight="1">
+    <row r="70" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="B70" s="11"/>
+        <v>72</v>
+      </c>
+      <c r="B70" s="15"/>
       <c r="C70" s="9" t="s">
         <v>16</v>
       </c>
@@ -5165,12 +5202,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" ht="29.25" hidden="1" customHeight="1">
+    <row r="71" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="B71" s="8">
-        <v>160.0</v>
+        <v>160</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>16</v>
@@ -5215,12 +5252,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" ht="29.25" hidden="1" customHeight="1">
+    <row r="72" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="B72" s="8">
-        <v>161.0</v>
+        <v>161</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>16</v>
@@ -5265,12 +5302,12 @@
         <v>214</v>
       </c>
     </row>
-    <row r="73" ht="29.25" hidden="1" customHeight="1">
+    <row r="73" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
-        <v>75.0</v>
-      </c>
-      <c r="B73" s="10">
-        <v>165.0</v>
+        <v>75</v>
+      </c>
+      <c r="B73" s="14">
+        <v>165</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>16</v>
@@ -5315,11 +5352,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" ht="29.25" hidden="1" customHeight="1">
+    <row r="74" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
-        <v>76.0</v>
-      </c>
-      <c r="B74" s="11"/>
+        <v>76</v>
+      </c>
+      <c r="B74" s="15"/>
       <c r="C74" s="9" t="s">
         <v>16</v>
       </c>
@@ -5363,12 +5400,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" ht="29.25" hidden="1" customHeight="1">
+    <row r="75" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
-        <v>77.0</v>
-      </c>
-      <c r="B75" s="10">
-        <v>166.0</v>
+        <v>77</v>
+      </c>
+      <c r="B75" s="14">
+        <v>166</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>16</v>
@@ -5413,11 +5450,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="76" ht="29.25" hidden="1" customHeight="1">
+    <row r="76" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
-        <v>78.0</v>
-      </c>
-      <c r="B76" s="11"/>
+        <v>78</v>
+      </c>
+      <c r="B76" s="15"/>
       <c r="C76" s="9" t="s">
         <v>16</v>
       </c>
@@ -5461,12 +5498,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="77" ht="29.25" hidden="1" customHeight="1">
+    <row r="77" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="B77" s="8">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>16</v>
@@ -5511,12 +5548,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" ht="29.25" hidden="1" customHeight="1">
+    <row r="78" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
-        <v>80.0</v>
-      </c>
-      <c r="B78" s="10">
-        <v>168.0</v>
+        <v>80</v>
+      </c>
+      <c r="B78" s="14">
+        <v>168</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>16</v>
@@ -5561,11 +5598,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" ht="29.25" hidden="1" customHeight="1">
+    <row r="79" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
-        <v>81.0</v>
-      </c>
-      <c r="B79" s="11"/>
+        <v>81</v>
+      </c>
+      <c r="B79" s="15"/>
       <c r="C79" s="9" t="s">
         <v>16</v>
       </c>
@@ -5609,12 +5646,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" ht="29.25" hidden="1" customHeight="1">
+    <row r="80" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="B80" s="8">
-        <v>169.0</v>
+        <v>169</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>16</v>
@@ -5659,12 +5696,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" ht="29.25" hidden="1" customHeight="1">
+    <row r="81" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="B81" s="8">
-        <v>170.0</v>
+        <v>170</v>
       </c>
       <c r="C81" s="9" t="s">
         <v>16</v>
@@ -5709,12 +5746,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" ht="29.25" hidden="1" customHeight="1">
+    <row r="82" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
-        <v>84.0</v>
-      </c>
-      <c r="B82" s="10">
-        <v>171.0</v>
+        <v>84</v>
+      </c>
+      <c r="B82" s="14">
+        <v>171</v>
       </c>
       <c r="C82" s="9" t="s">
         <v>16</v>
@@ -5759,11 +5796,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" ht="29.25" hidden="1" customHeight="1">
+    <row r="83" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
-        <v>85.0</v>
-      </c>
-      <c r="B83" s="11"/>
+        <v>85</v>
+      </c>
+      <c r="B83" s="15"/>
       <c r="C83" s="9" t="s">
         <v>16</v>
       </c>
@@ -5807,12 +5844,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" ht="29.25" hidden="1" customHeight="1">
+    <row r="84" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="B84" s="8">
-        <v>201.0</v>
+        <v>201</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>16</v>
@@ -5857,12 +5894,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="85" ht="29.25" hidden="1" customHeight="1">
+    <row r="85" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
-        <v>87.0</v>
-      </c>
-      <c r="B85" s="10">
-        <v>202.0</v>
+        <v>87</v>
+      </c>
+      <c r="B85" s="14">
+        <v>202</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>16</v>
@@ -5907,11 +5944,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" ht="29.25" customHeight="1">
+    <row r="86" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
-        <v>88.0</v>
-      </c>
-      <c r="B86" s="11"/>
+        <v>88</v>
+      </c>
+      <c r="B86" s="15"/>
       <c r="C86" s="5" t="s">
         <v>16</v>
       </c>
@@ -5955,12 +5992,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" ht="29.25" hidden="1" customHeight="1">
+    <row r="87" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
-        <v>89.0</v>
-      </c>
-      <c r="B87" s="10">
-        <v>207.0</v>
+        <v>89</v>
+      </c>
+      <c r="B87" s="14">
+        <v>207</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>16</v>
@@ -6005,11 +6042,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" ht="29.25" hidden="1" customHeight="1">
+    <row r="88" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
-        <v>90.0</v>
-      </c>
-      <c r="B88" s="11"/>
+        <v>90</v>
+      </c>
+      <c r="B88" s="15"/>
       <c r="C88" s="9" t="s">
         <v>16</v>
       </c>
@@ -6053,12 +6090,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" ht="29.25" hidden="1" customHeight="1">
+    <row r="89" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
-        <v>91.0</v>
-      </c>
-      <c r="B89" s="10">
-        <v>224.0</v>
+        <v>91</v>
+      </c>
+      <c r="B89" s="14">
+        <v>224</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>16</v>
@@ -6103,11 +6140,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" ht="29.25" hidden="1" customHeight="1">
+    <row r="90" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
-        <v>92.0</v>
-      </c>
-      <c r="B90" s="11"/>
+        <v>92</v>
+      </c>
+      <c r="B90" s="15"/>
       <c r="C90" s="9" t="s">
         <v>16</v>
       </c>
@@ -6151,12 +6188,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="91" ht="29.25" hidden="1" customHeight="1">
+    <row r="91" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
-        <v>93.0</v>
-      </c>
-      <c r="B91" s="10">
-        <v>230.0</v>
+        <v>93</v>
+      </c>
+      <c r="B91" s="14">
+        <v>230</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>16</v>
@@ -6201,9 +6238,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" ht="29.25" hidden="1" customHeight="1">
+    <row r="92" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7"/>
-      <c r="B92" s="11"/>
+      <c r="B92" s="15"/>
       <c r="C92" s="9" t="s">
         <v>16</v>
       </c>
@@ -6247,12 +6284,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" ht="29.25" hidden="1" customHeight="1">
+    <row r="93" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
-        <v>94.0</v>
-      </c>
-      <c r="B93" s="10">
-        <v>234.0</v>
+        <v>94</v>
+      </c>
+      <c r="B93" s="14">
+        <v>234</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>16</v>
@@ -6297,11 +6334,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" ht="29.25" hidden="1" customHeight="1">
+    <row r="94" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
-        <v>95.0</v>
-      </c>
-      <c r="B94" s="11"/>
+        <v>95</v>
+      </c>
+      <c r="B94" s="15"/>
       <c r="C94" s="9" t="s">
         <v>16</v>
       </c>
@@ -6345,12 +6382,12 @@
         <v>257</v>
       </c>
     </row>
-    <row r="95" ht="29.25" hidden="1" customHeight="1">
+    <row r="95" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
-        <v>96.0</v>
-      </c>
-      <c r="B95" s="10">
-        <v>255.0</v>
+        <v>96</v>
+      </c>
+      <c r="B95" s="14">
+        <v>255</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>16</v>
@@ -6395,11 +6432,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" ht="29.25" hidden="1" customHeight="1">
+    <row r="96" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
-        <v>97.0</v>
-      </c>
-      <c r="B96" s="12"/>
+        <v>97</v>
+      </c>
+      <c r="B96" s="16"/>
       <c r="C96" s="9" t="s">
         <v>16</v>
       </c>
@@ -6443,11 +6480,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="97" ht="29.25" customHeight="1">
+    <row r="97" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
-        <v>98.0</v>
-      </c>
-      <c r="B97" s="11"/>
+        <v>98</v>
+      </c>
+      <c r="B97" s="15"/>
       <c r="C97" s="5" t="s">
         <v>16</v>
       </c>
@@ -6491,12 +6528,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" ht="29.25" customHeight="1">
+    <row r="98" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="B98" s="8">
-        <v>256.0</v>
+        <v>256</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>16</v>
@@ -6541,12 +6578,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" ht="29.25" customHeight="1">
+    <row r="99" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="B99" s="8">
-        <v>260.0</v>
+        <v>260</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>16</v>
@@ -6591,12 +6628,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" ht="29.25" hidden="1" customHeight="1">
+    <row r="100" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
-        <v>101.0</v>
-      </c>
-      <c r="B100" s="10">
-        <v>263.0</v>
+        <v>101</v>
+      </c>
+      <c r="B100" s="14">
+        <v>263</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>16</v>
@@ -6641,11 +6678,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" ht="29.25" hidden="1" customHeight="1">
+    <row r="101" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
-        <v>102.0</v>
-      </c>
-      <c r="B101" s="12"/>
+        <v>102</v>
+      </c>
+      <c r="B101" s="16"/>
       <c r="C101" s="9" t="s">
         <v>16</v>
       </c>
@@ -6689,11 +6726,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="102" ht="29.25" hidden="1" customHeight="1">
+    <row r="102" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
-        <v>103.0</v>
-      </c>
-      <c r="B102" s="12"/>
+        <v>103</v>
+      </c>
+      <c r="B102" s="16"/>
       <c r="C102" s="9" t="s">
         <v>16</v>
       </c>
@@ -6737,11 +6774,11 @@
         <v>269</v>
       </c>
     </row>
-    <row r="103" ht="29.25" hidden="1" customHeight="1">
+    <row r="103" spans="1:16" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
-        <v>104.0</v>
-      </c>
-      <c r="B103" s="11"/>
+        <v>104</v>
+      </c>
+      <c r="B103" s="15"/>
       <c r="C103" s="9" t="s">
         <v>16</v>
       </c>
@@ -6785,12 +6822,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" ht="29.25" customHeight="1">
+    <row r="104" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="B104" s="8">
-        <v>268.0</v>
+        <v>268</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>16</v>
@@ -6835,12 +6872,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="105" ht="14.25" hidden="1" customHeight="1">
+    <row r="105" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="B105" s="8">
-        <v>269.0</v>
+        <v>269</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>16</v>
@@ -6885,12 +6922,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="106" ht="14.25" hidden="1" customHeight="1">
+    <row r="106" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
-        <v>107.0</v>
-      </c>
-      <c r="B106" s="10">
-        <v>270.0</v>
+        <v>107</v>
+      </c>
+      <c r="B106" s="14">
+        <v>270</v>
       </c>
       <c r="C106" s="9" t="s">
         <v>16</v>
@@ -6935,11 +6972,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
-        <v>108.0</v>
-      </c>
-      <c r="B107" s="11"/>
+        <v>108</v>
+      </c>
+      <c r="B107" s="15"/>
       <c r="C107" s="5" t="s">
         <v>16</v>
       </c>
@@ -6983,12 +7020,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" ht="14.25" hidden="1" customHeight="1">
+    <row r="108" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
-        <v>109.0</v>
+        <v>109</v>
       </c>
       <c r="B108" s="8">
-        <v>272.0</v>
+        <v>272</v>
       </c>
       <c r="C108" s="9" t="s">
         <v>16</v>
@@ -7033,12 +7070,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" ht="14.25" hidden="1" customHeight="1">
+    <row r="109" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
-        <v>110.0</v>
-      </c>
-      <c r="B109" s="10">
-        <v>274.0</v>
+        <v>110</v>
+      </c>
+      <c r="B109" s="14">
+        <v>274</v>
       </c>
       <c r="C109" s="9" t="s">
         <v>16</v>
@@ -7083,11 +7120,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="110" ht="14.25" hidden="1" customHeight="1">
+    <row r="110" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
-        <v>111.0</v>
-      </c>
-      <c r="B110" s="11"/>
+        <v>111</v>
+      </c>
+      <c r="B110" s="15"/>
       <c r="C110" s="9" t="s">
         <v>16</v>
       </c>
@@ -7131,12 +7168,12 @@
         <v>289</v>
       </c>
     </row>
-    <row r="111" ht="14.25" hidden="1" customHeight="1">
+    <row r="111" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
-        <v>112.0</v>
-      </c>
-      <c r="B111" s="10">
-        <v>276.0</v>
+        <v>112</v>
+      </c>
+      <c r="B111" s="14">
+        <v>276</v>
       </c>
       <c r="C111" s="9" t="s">
         <v>16</v>
@@ -7181,9 +7218,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7"/>
-      <c r="B112" s="11"/>
+      <c r="B112" s="15"/>
       <c r="C112" s="5" t="s">
         <v>16</v>
       </c>
@@ -7227,12 +7264,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="113" ht="14.25" hidden="1" customHeight="1">
+    <row r="113" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
-        <v>113.0</v>
-      </c>
-      <c r="B113" s="10">
-        <v>277.0</v>
+        <v>113</v>
+      </c>
+      <c r="B113" s="14">
+        <v>277</v>
       </c>
       <c r="C113" s="9" t="s">
         <v>16</v>
@@ -7277,11 +7314,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
-        <v>114.0</v>
-      </c>
-      <c r="B114" s="11"/>
+        <v>114</v>
+      </c>
+      <c r="B114" s="15"/>
       <c r="C114" s="5" t="s">
         <v>16</v>
       </c>
@@ -7325,12 +7362,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" ht="14.25" hidden="1" customHeight="1">
+    <row r="115" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
-        <v>115.0</v>
-      </c>
-      <c r="B115" s="10">
-        <v>278.0</v>
+        <v>115</v>
+      </c>
+      <c r="B115" s="14">
+        <v>278</v>
       </c>
       <c r="C115" s="9" t="s">
         <v>16</v>
@@ -7375,11 +7412,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" ht="14.25" hidden="1" customHeight="1">
+    <row r="116" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
-        <v>116.0</v>
-      </c>
-      <c r="B116" s="12"/>
+        <v>116</v>
+      </c>
+      <c r="B116" s="16"/>
       <c r="C116" s="9" t="s">
         <v>16</v>
       </c>
@@ -7423,11 +7460,11 @@
         <v>303</v>
       </c>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="13">
-        <v>117.0</v>
-      </c>
-      <c r="B117" s="11"/>
+    <row r="117" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="10">
+        <v>117</v>
+      </c>
+      <c r="B117" s="15"/>
       <c r="C117" s="5" t="s">
         <v>16</v>
       </c>
@@ -7471,12 +7508,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" ht="14.25" hidden="1" customHeight="1">
-      <c r="A118" s="13">
-        <v>118.0</v>
-      </c>
-      <c r="B118" s="10">
-        <v>279.0</v>
+    <row r="118" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="10">
+        <v>118</v>
+      </c>
+      <c r="B118" s="14">
+        <v>279</v>
       </c>
       <c r="C118" s="9" t="s">
         <v>16</v>
@@ -7521,9 +7558,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" ht="14.25" hidden="1" customHeight="1">
-      <c r="A119" s="14"/>
-      <c r="B119" s="12"/>
+    <row r="119" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="11"/>
+      <c r="B119" s="16"/>
       <c r="C119" s="9" t="s">
         <v>16</v>
       </c>
@@ -7567,8 +7604,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
-      <c r="B120" s="11"/>
+    <row r="120" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="15"/>
       <c r="C120" s="5" t="s">
         <v>16</v>
       </c>
@@ -7612,9 +7649,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" ht="14.25" hidden="1" customHeight="1">
-      <c r="B121" s="10">
-        <v>281.0</v>
+    <row r="121" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="14">
+        <v>281</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>16</v>
@@ -7659,8 +7696,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
-      <c r="B122" s="11"/>
+    <row r="122" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="15"/>
       <c r="C122" s="5" t="s">
         <v>16</v>
       </c>
@@ -7704,9 +7741,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" ht="14.25" hidden="1" customHeight="1">
-      <c r="B123" s="10">
-        <v>285.0</v>
+    <row r="123" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="14">
+        <v>285</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>16</v>
@@ -7751,8 +7788,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
-      <c r="B124" s="11"/>
+    <row r="124" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="15"/>
       <c r="C124" s="5" t="s">
         <v>16</v>
       </c>
@@ -7796,9 +7833,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" ht="14.25" hidden="1" customHeight="1">
+    <row r="125" spans="1:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="8">
-        <v>286.0</v>
+        <v>286</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>16</v>
@@ -7843,9 +7880,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="8">
-        <v>287.0</v>
+        <v>287</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>16</v>
@@ -7890,9 +7927,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="8">
-        <v>288.0</v>
+        <v>288</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>16</v>
@@ -7937,9 +7974,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="8">
-        <v>289.0</v>
+        <v>289</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>16</v>
@@ -7984,9 +8021,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="8">
-        <v>293.0</v>
+        <v>293</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>16</v>
@@ -8031,9 +8068,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="8">
-        <v>294.0</v>
+        <v>294</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>16</v>
@@ -8078,2593 +8115,2563 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
-      <c r="B131" s="15" t="s">
+    <row r="131" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="12" t="s">
         <v>339</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D131" s="16" t="s">
+      <c r="D131" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E131" s="16" t="s">
+      <c r="E131" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="F131" s="16" t="s">
+      <c r="F131" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="G131" s="16" t="s">
+      <c r="G131" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H131" s="16" t="s">
+      <c r="H131" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I131" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J131" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K131" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L131" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M131" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N131" s="16" t="s">
+      <c r="I131" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J131" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K131" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L131" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M131" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N131" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O131" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P131" s="16" t="s">
+      <c r="O131" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P131" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="17" t="s">
         <v>343</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D132" s="16" t="s">
+      <c r="D132" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="E132" s="16" t="s">
+      <c r="E132" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F132" s="16" t="s">
+      <c r="F132" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="G132" s="16" t="s">
+      <c r="G132" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H132" s="16" t="s">
+      <c r="H132" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I132" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J132" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K132" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L132" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M132" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N132" s="16" t="s">
+      <c r="I132" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J132" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K132" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L132" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M132" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N132" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O132" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P132" s="16" t="s">
+      <c r="O132" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P132" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="133" ht="14.25" hidden="1" customHeight="1">
-      <c r="B133" s="11"/>
-      <c r="C133" s="16" t="s">
+    <row r="133" spans="2:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B133" s="15"/>
+      <c r="C133" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D133" s="16" t="s">
+      <c r="D133" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="E133" s="16" t="s">
+      <c r="E133" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F133" s="16" t="s">
+      <c r="F133" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="G133" s="16" t="s">
+      <c r="G133" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H133" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I133" s="16" t="s">
+      <c r="H133" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I133" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="J133" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K133" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L133" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M133" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N133" s="16" t="s">
+      <c r="J133" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K133" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L133" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M133" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N133" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="O133" s="16" t="s">
+      <c r="O133" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="P133" s="16" t="s">
+      <c r="P133" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="17" t="s">
         <v>347</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D134" s="16" t="s">
+      <c r="D134" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="E134" s="16" t="s">
+      <c r="E134" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="F134" s="16" t="s">
+      <c r="F134" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="G134" s="16" t="s">
+      <c r="G134" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H134" s="16" t="s">
+      <c r="H134" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I134" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J134" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K134" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L134" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M134" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N134" s="16" t="s">
+      <c r="I134" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J134" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K134" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L134" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M134" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N134" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O134" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P134" s="16" t="s">
+      <c r="O134" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P134" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
-      <c r="B135" s="11"/>
+    <row r="135" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B135" s="15"/>
       <c r="C135" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D135" s="16" t="s">
+      <c r="D135" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E135" s="16" t="s">
+      <c r="E135" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="F135" s="16" t="s">
+      <c r="F135" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="G135" s="16" t="s">
+      <c r="G135" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="H135" s="16" t="s">
+      <c r="H135" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="I135" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J135" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K135" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L135" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M135" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N135" s="16" t="s">
+      <c r="I135" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J135" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K135" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L135" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M135" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N135" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O135" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P135" s="16" t="s">
+      <c r="O135" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P135" s="13" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
-      <c r="B136" s="15" t="s">
+    <row r="136" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D136" s="16" t="s">
+      <c r="D136" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E136" s="16" t="s">
+      <c r="E136" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="F136" s="16" t="s">
+      <c r="F136" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="G136" s="16" t="s">
+      <c r="G136" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H136" s="16" t="s">
+      <c r="H136" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="I136" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J136" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K136" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L136" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M136" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N136" s="16" t="s">
+      <c r="I136" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J136" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K136" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L136" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M136" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N136" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O136" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P136" s="16" t="s">
+      <c r="O136" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P136" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
-      <c r="B137" s="15">
-        <v>22.0</v>
+    <row r="137" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B137" s="12">
+        <v>22</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D137" s="16" t="s">
+      <c r="D137" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E137" s="16" t="s">
+      <c r="E137" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="F137" s="16" t="s">
+      <c r="F137" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="G137" s="16" t="s">
+      <c r="G137" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H137" s="16" t="s">
+      <c r="H137" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I137" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J137" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K137" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L137" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M137" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N137" s="16" t="s">
+      <c r="I137" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J137" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K137" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L137" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M137" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N137" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O137" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P137" s="16" t="s">
+      <c r="O137" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P137" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
-      <c r="B138" s="15">
-        <v>34.0</v>
+    <row r="138" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B138" s="12">
+        <v>34</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D138" s="16" t="s">
+      <c r="D138" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E138" s="16" t="s">
+      <c r="E138" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="F138" s="16" t="s">
+      <c r="F138" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="G138" s="16" t="s">
+      <c r="G138" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H138" s="16" t="s">
+      <c r="H138" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I138" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J138" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K138" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L138" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M138" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N138" s="16" t="s">
+      <c r="I138" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J138" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K138" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L138" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M138" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N138" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O138" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P138" s="16" t="s">
+      <c r="O138" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P138" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
-      <c r="B139" s="15">
-        <v>120.0</v>
+    <row r="139" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B139" s="12">
+        <v>120</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D139" s="16" t="s">
+      <c r="D139" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="E139" s="16" t="s">
+      <c r="E139" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="F139" s="16" t="s">
+      <c r="F139" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="G139" s="16" t="s">
+      <c r="G139" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H139" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I139" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J139" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K139" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L139" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M139" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N139" s="16" t="s">
+      <c r="H139" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I139" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J139" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K139" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L139" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M139" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N139" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O139" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P139" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="140" ht="14.25" customHeight="1">
-      <c r="B140" s="15">
-        <v>121.0</v>
+      <c r="O139" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P139" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="12">
+        <v>121</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D140" s="16" t="s">
+      <c r="D140" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="E140" s="16" t="s">
+      <c r="E140" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="F140" s="16" t="s">
+      <c r="F140" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="G140" s="16" t="s">
+      <c r="G140" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H140" s="16" t="s">
+      <c r="H140" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I140" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J140" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K140" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L140" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M140" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N140" s="16" t="s">
+      <c r="I140" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J140" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K140" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L140" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M140" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N140" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O140" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P140" s="16" t="s">
+      <c r="O140" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P140" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
-      <c r="B141" s="15">
-        <v>131.0</v>
+    <row r="141" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B141" s="12">
+        <v>131</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D141" s="16" t="s">
+      <c r="D141" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="E141" s="16" t="s">
+      <c r="E141" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="F141" s="16" t="s">
+      <c r="F141" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="G141" s="16" t="s">
+      <c r="G141" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H141" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I141" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J141" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K141" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L141" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M141" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N141" s="16" t="s">
+      <c r="H141" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I141" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J141" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K141" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L141" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M141" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N141" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O141" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P141" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="142" ht="14.25" customHeight="1">
-      <c r="B142" s="15">
-        <v>132.0</v>
+      <c r="O141" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P141" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B142" s="12">
+        <v>132</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D142" s="16" t="s">
+      <c r="D142" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="E142" s="16" t="s">
+      <c r="E142" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="F142" s="16" t="s">
+      <c r="F142" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="G142" s="16" t="s">
+      <c r="G142" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H142" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I142" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J142" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K142" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L142" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M142" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N142" s="16" t="s">
+      <c r="H142" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I142" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J142" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K142" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L142" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M142" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N142" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O142" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P142" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="143" ht="14.25" customHeight="1">
-      <c r="B143" s="15">
-        <v>133.0</v>
+      <c r="O142" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P142" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B143" s="12">
+        <v>133</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D143" s="16" t="s">
+      <c r="D143" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="E143" s="16" t="s">
+      <c r="E143" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="F143" s="16" t="s">
+      <c r="F143" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="G143" s="16" t="s">
+      <c r="G143" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H143" s="16" t="s">
+      <c r="H143" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="I143" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J143" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K143" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L143" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M143" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N143" s="16" t="s">
+      <c r="I143" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J143" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K143" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L143" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M143" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N143" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O143" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P143" s="16" t="s">
+      <c r="O143" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P143" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
-      <c r="B144" s="15">
-        <v>135.0</v>
+    <row r="144" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B144" s="12">
+        <v>135</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D144" s="16" t="s">
+      <c r="D144" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="E144" s="16" t="s">
+      <c r="E144" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="F144" s="16" t="s">
+      <c r="F144" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="G144" s="16" t="s">
+      <c r="G144" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H144" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I144" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J144" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K144" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L144" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M144" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N144" s="16" t="s">
+      <c r="H144" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I144" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J144" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K144" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L144" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M144" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N144" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O144" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P144" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="145" ht="14.25" customHeight="1">
-      <c r="B145" s="15">
-        <v>152.0</v>
+      <c r="O144" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P144" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B145" s="12">
+        <v>152</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D145" s="16" t="s">
+      <c r="D145" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="E145" s="16" t="s">
+      <c r="E145" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="F145" s="16" t="s">
+      <c r="F145" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="G145" s="16" t="s">
+      <c r="G145" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H145" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I145" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J145" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K145" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L145" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M145" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N145" s="16" t="s">
+      <c r="H145" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I145" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J145" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K145" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L145" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M145" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N145" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O145" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P145" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="146" ht="14.25" customHeight="1">
-      <c r="B146" s="15">
-        <v>153.0</v>
+      <c r="O145" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P145" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B146" s="12">
+        <v>153</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D146" s="16" t="s">
+      <c r="D146" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="E146" s="16" t="s">
+      <c r="E146" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="F146" s="16" t="s">
+      <c r="F146" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="G146" s="16" t="s">
+      <c r="G146" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H146" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I146" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J146" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K146" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L146" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M146" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N146" s="16" t="s">
+      <c r="H146" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I146" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J146" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K146" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L146" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M146" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N146" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O146" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P146" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="147" ht="14.25" customHeight="1">
-      <c r="B147" s="15">
-        <v>155.0</v>
+      <c r="O146" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P146" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B147" s="12">
+        <v>155</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D147" s="16" t="s">
+      <c r="D147" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="E147" s="16" t="s">
+      <c r="E147" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="F147" s="16" t="s">
+      <c r="F147" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="G147" s="16" t="s">
+      <c r="G147" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H147" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I147" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J147" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K147" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L147" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M147" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N147" s="16" t="s">
+      <c r="H147" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I147" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J147" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K147" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L147" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M147" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N147" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O147" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P147" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="148" ht="14.25" customHeight="1">
+      <c r="O147" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P147" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="17">
-        <v>157.0</v>
+        <v>157</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D148" s="16" t="s">
+      <c r="D148" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="E148" s="16" t="s">
+      <c r="E148" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="F148" s="16" t="s">
+      <c r="F148" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="G148" s="16" t="s">
+      <c r="G148" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H148" s="16" t="s">
+      <c r="H148" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I148" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J148" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K148" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L148" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M148" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N148" s="16" t="s">
+      <c r="I148" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J148" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K148" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L148" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M148" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N148" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O148" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P148" s="16" t="s">
+      <c r="O148" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P148" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
-      <c r="B149" s="11"/>
+    <row r="149" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B149" s="15"/>
       <c r="C149" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D149" s="16" t="s">
+      <c r="D149" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="E149" s="16" t="s">
+      <c r="E149" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="F149" s="16" t="s">
+      <c r="F149" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="G149" s="16" t="s">
+      <c r="G149" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H149" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I149" s="16" t="s">
+      <c r="H149" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I149" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="J149" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K149" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L149" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M149" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N149" s="16" t="s">
+      <c r="J149" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K149" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L149" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M149" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N149" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O149" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P149" s="16" t="s">
+      <c r="O149" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P149" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
-      <c r="B150" s="15">
-        <v>159.0</v>
+    <row r="150" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="12">
+        <v>159</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D150" s="16" t="s">
+      <c r="D150" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="E150" s="16" t="s">
+      <c r="E150" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="F150" s="16" t="s">
+      <c r="F150" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="G150" s="16" t="s">
+      <c r="G150" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H150" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I150" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J150" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K150" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L150" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M150" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N150" s="16" t="s">
+      <c r="H150" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J150" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K150" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L150" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M150" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N150" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O150" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P150" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="151" ht="14.25" customHeight="1">
-      <c r="B151" s="15">
-        <v>162.0</v>
+      <c r="O150" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P150" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="151" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B151" s="12">
+        <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D151" s="16" t="s">
+      <c r="D151" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="E151" s="16" t="s">
+      <c r="E151" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="F151" s="16" t="s">
+      <c r="F151" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="G151" s="16" t="s">
+      <c r="G151" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H151" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I151" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J151" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K151" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L151" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M151" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N151" s="16" t="s">
+      <c r="H151" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I151" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J151" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K151" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L151" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M151" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N151" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O151" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P151" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="152" ht="14.25" customHeight="1">
+      <c r="O151" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P151" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="17">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D152" s="16" t="s">
+      <c r="D152" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="E152" s="16" t="s">
+      <c r="E152" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="F152" s="16" t="s">
+      <c r="F152" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="G152" s="16" t="s">
+      <c r="G152" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H152" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I152" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J152" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K152" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L152" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M152" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N152" s="16" t="s">
+      <c r="H152" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J152" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K152" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L152" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M152" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N152" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O152" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P152" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="153" ht="14.25" hidden="1" customHeight="1">
-      <c r="B153" s="11"/>
-      <c r="C153" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D153" s="16" t="s">
+      <c r="O152" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P152" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="153" spans="2:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B153" s="15"/>
+      <c r="C153" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D153" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="E153" s="16" t="s">
+      <c r="E153" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="F153" s="16" t="s">
+      <c r="F153" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="G153" s="16" t="s">
+      <c r="G153" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H153" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I153" s="16" t="s">
+      <c r="H153" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I153" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="J153" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K153" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L153" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M153" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N153" s="16" t="s">
+      <c r="J153" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K153" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L153" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M153" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N153" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="O153" s="16" t="s">
+      <c r="O153" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="P153" s="16" t="s">
+      <c r="P153" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
-      <c r="B154" s="15">
-        <v>171.0</v>
+    <row r="154" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B154" s="12">
+        <v>171</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D154" s="16" t="s">
+      <c r="D154" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="E154" s="16" t="s">
+      <c r="E154" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="F154" s="16" t="s">
+      <c r="F154" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="G154" s="16" t="s">
+      <c r="G154" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H154" s="16" t="s">
+      <c r="H154" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I154" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J154" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K154" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L154" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M154" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N154" s="16" t="s">
+      <c r="I154" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J154" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K154" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L154" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M154" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N154" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O154" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P154" s="16" t="s">
+      <c r="O154" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P154" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
-      <c r="B155" s="15">
-        <v>206.0</v>
+    <row r="155" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B155" s="12">
+        <v>206</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D155" s="16" t="s">
+      <c r="D155" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="E155" s="16" t="s">
+      <c r="E155" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="F155" s="16" t="s">
+      <c r="F155" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="G155" s="16" t="s">
+      <c r="G155" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H155" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I155" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J155" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K155" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L155" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M155" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N155" s="16" t="s">
+      <c r="H155" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I155" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J155" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K155" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L155" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M155" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N155" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O155" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P155" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="156" ht="14.25" customHeight="1">
-      <c r="B156" s="15">
-        <v>208.0</v>
+      <c r="O155" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P155" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B156" s="12">
+        <v>208</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D156" s="16" t="s">
+      <c r="D156" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="E156" s="16" t="s">
+      <c r="E156" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="F156" s="16" t="s">
+      <c r="F156" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="G156" s="16" t="s">
+      <c r="G156" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H156" s="16" t="s">
+      <c r="H156" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="I156" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J156" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K156" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L156" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M156" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N156" s="16" t="s">
+      <c r="I156" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J156" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K156" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L156" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M156" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N156" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O156" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P156" s="16" t="s">
+      <c r="O156" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P156" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
-      <c r="B157" s="15">
-        <v>211.0</v>
+    <row r="157" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B157" s="12">
+        <v>211</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D157" s="16" t="s">
+      <c r="D157" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="E157" s="16" t="s">
+      <c r="E157" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="F157" s="16" t="s">
+      <c r="F157" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="G157" s="16" t="s">
+      <c r="G157" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H157" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I157" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J157" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K157" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L157" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M157" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N157" s="16" t="s">
+      <c r="H157" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I157" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J157" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K157" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L157" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M157" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N157" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O157" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P157" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="158" ht="14.25" customHeight="1">
-      <c r="B158" s="15">
-        <v>221.0</v>
+      <c r="O157" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P157" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B158" s="12">
+        <v>221</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D158" s="16" t="s">
+      <c r="D158" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="E158" s="16" t="s">
+      <c r="E158" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="F158" s="16" t="s">
+      <c r="F158" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="G158" s="16" t="s">
+      <c r="G158" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H158" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I158" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J158" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K158" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L158" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M158" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N158" s="16" t="s">
+      <c r="H158" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I158" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J158" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K158" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L158" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M158" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N158" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O158" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P158" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="159" ht="14.25" customHeight="1">
+      <c r="O158" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P158" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="17">
-        <v>229.0</v>
+        <v>229</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D159" s="16" t="s">
+      <c r="D159" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="E159" s="16" t="s">
+      <c r="E159" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="F159" s="16" t="s">
+      <c r="F159" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="G159" s="16" t="s">
+      <c r="G159" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H159" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I159" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J159" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K159" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L159" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M159" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N159" s="16" t="s">
+      <c r="H159" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I159" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J159" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K159" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L159" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M159" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N159" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O159" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P159" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="160" ht="14.25" hidden="1" customHeight="1">
-      <c r="B160" s="11"/>
-      <c r="C160" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D160" s="16" t="s">
+      <c r="O159" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P159" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="2:16" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="15"/>
+      <c r="C160" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D160" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="E160" s="16" t="s">
+      <c r="E160" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="F160" s="16" t="s">
+      <c r="F160" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="G160" s="16" t="s">
+      <c r="G160" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H160" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I160" s="16" t="s">
+      <c r="H160" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="J160" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K160" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L160" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M160" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N160" s="16" t="s">
+      <c r="J160" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K160" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L160" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M160" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N160" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="O160" s="16" t="s">
+      <c r="O160" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="P160" s="16" t="s">
+      <c r="P160" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
-      <c r="B161" s="15">
-        <v>236.0</v>
+    <row r="161" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B161" s="12">
+        <v>236</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D161" s="16" t="s">
+      <c r="D161" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="E161" s="16" t="s">
+      <c r="E161" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="F161" s="16" t="s">
+      <c r="F161" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="G161" s="16" t="s">
+      <c r="G161" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H161" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I161" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J161" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K161" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L161" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M161" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N161" s="16" t="s">
+      <c r="H161" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I161" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J161" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K161" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L161" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M161" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N161" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O161" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P161" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="162" ht="14.25" customHeight="1">
-      <c r="B162" s="15">
-        <v>252.0</v>
+      <c r="O161" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P161" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B162" s="12">
+        <v>252</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D162" s="16" t="s">
+      <c r="D162" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="E162" s="16" t="s">
+      <c r="E162" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="F162" s="16" t="s">
+      <c r="F162" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="G162" s="16" t="s">
+      <c r="G162" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H162" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I162" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J162" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K162" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L162" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M162" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N162" s="16" t="s">
+      <c r="H162" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I162" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J162" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K162" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L162" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M162" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N162" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O162" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P162" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="163" ht="14.25" customHeight="1">
-      <c r="B163" s="15">
-        <v>263.0</v>
+      <c r="O162" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P162" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="12">
+        <v>263</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D163" s="16" t="s">
+      <c r="D163" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="E163" s="16" t="s">
+      <c r="E163" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="F163" s="16" t="s">
+      <c r="F163" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="G163" s="16" t="s">
+      <c r="G163" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H163" s="16" t="s">
+      <c r="H163" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I163" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J163" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K163" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L163" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M163" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N163" s="16" t="s">
+      <c r="I163" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J163" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K163" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L163" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M163" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N163" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O163" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P163" s="16" t="s">
+      <c r="O163" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P163" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
-      <c r="B164" s="15">
-        <v>266.0</v>
+    <row r="164" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B164" s="12">
+        <v>266</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D164" s="16" t="s">
+      <c r="D164" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E164" s="16" t="s">
+      <c r="E164" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="F164" s="16" t="s">
+      <c r="F164" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="G164" s="16" t="s">
+      <c r="G164" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H164" s="16" t="s">
+      <c r="H164" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I164" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J164" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K164" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L164" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M164" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N164" s="16" t="s">
+      <c r="I164" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J164" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K164" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L164" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M164" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N164" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O164" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P164" s="16" t="s">
+      <c r="O164" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P164" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
-      <c r="B165" s="15">
-        <v>272.0</v>
+    <row r="165" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="12">
+        <v>272</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D165" s="16" t="s">
+      <c r="D165" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="E165" s="16" t="s">
+      <c r="E165" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="F165" s="16" t="s">
+      <c r="F165" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="G165" s="16" t="s">
+      <c r="G165" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H165" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I165" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J165" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K165" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L165" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="M165" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="N165" s="16" t="s">
+      <c r="H165" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I165" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J165" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K165" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L165" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M165" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N165" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="O165" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="P165" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="166" ht="14.25" customHeight="1">
+      <c r="O165" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P165" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C166" s="5"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C167" s="5"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="168" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="$B$2:$P$165">
+  <autoFilter ref="B2:P165" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
+        <filter val="03-09-2026 09:00PM"/>
+        <filter val="03-09-2026 09:09PM"/>
+        <filter val="03-09-2026 09:10PM"/>
+        <filter val="03-09-2026 09:11PM"/>
+        <filter val="03-09-2026 09:13PM"/>
+        <filter val="03-09-2026 09:15PM"/>
+        <filter val="03-09-2026 09:16PM"/>
+        <filter val="03-09-2026 09:17PM"/>
+        <filter val="03-09-2026 09:19PM"/>
+        <filter val="03-09-2026 09:20PM"/>
+        <filter val="03-09-2026 09:23PM"/>
+        <filter val="03-09-2026 09:24PM"/>
+        <filter val="03-09-2026 09:26PM"/>
+        <filter val="03-09-2026 09:27PM"/>
+        <filter val="03-09-2026 09:32PM"/>
+        <filter val="03-09-2026 09:35PM"/>
+        <filter val="03-09-2026 09:36PM"/>
+        <filter val="03-09-2026 09:37PM"/>
+        <filter val="03-09-2026 09:39PM"/>
+        <filter val="03-09-2026 09:40PM"/>
+        <filter val="03-09-2026 09:41PM"/>
+        <filter val="03-09-2026 09:43PM"/>
+        <filter val="03-09-2026 09:45PM"/>
+        <filter val="03-09-2026 09:51PM"/>
+        <filter val="03-09-2026 09:53PM"/>
+        <filter val="03-09-2026 09:58PM"/>
+        <filter val="03-09-2026 10:01PM"/>
+        <filter val="03-09-2026 10:03PM"/>
+        <filter val="03-09-2026 10:24PM"/>
+        <filter val="03-09-2026 10:25PM"/>
+        <filter val="03-09-2026 10:26PM"/>
+        <filter val="03-09-2026 10:27PM"/>
+        <filter val="03-09-2026 10:29PM"/>
+        <filter val="03-09-2026 10:48PM"/>
+        <filter val="03-09-2026 10:55PM"/>
+        <filter val="03-09-2026 10:57PM"/>
+        <filter val="03-09-2026 11:09PM"/>
         <filter val="03-09-2026 11:10PM"/>
+        <filter val="03-09-2026 11:13PM"/>
+        <filter val="03-09-2026 11:15PM"/>
+        <filter val="03-09-2026 11:23PM"/>
+        <filter val="03-09-2026 11:26PM"/>
+        <filter val="03-09-2026 11:29PM"/>
+        <filter val="03-09-2026 11:32PM"/>
+        <filter val="03-09-2026 11:34PM"/>
+        <filter val="03-09-2026 11:51PM"/>
+        <filter val="03-10-2026 01:07AM"/>
+        <filter val="03-10-2026 01:19AM"/>
         <filter val="03-10-2026 01:23AM"/>
+        <filter val="03-10-2026 01:26AM"/>
         <filter val="03-10-2026 01:46AM"/>
-        <filter val="03-09-2026 09:37PM"/>
-        <filter val="03-09-2026 09:10PM"/>
-        <filter val="03-09-2026 11:29PM"/>
+        <filter val="03-10-2026 02:37AM"/>
+        <filter val="03-10-2026 03:21AM"/>
         <filter val="03-10-2026 03:42AM"/>
+        <filter val="03-10-2026 04:14AM"/>
+        <filter val="03-10-2026 04:15AM"/>
+        <filter val="03-10-2026 04:29AM"/>
+        <filter val="03-10-2026 05:56AM"/>
+        <filter val="03-10-2026 06:05AM"/>
+        <filter val="03-10-2026 06:20AM"/>
+        <filter val="03-10-2026 06:41AM"/>
+        <filter val="03-10-2026 06:51AM"/>
+        <filter val="03-10-2026 06:55AM"/>
+        <filter val="03-10-2026 07:31AM"/>
+        <filter val="03-10-2026 08:19AM"/>
+        <filter val="03-10-2026 12:05AM"/>
+        <filter val="03-10-2026 12:31AM"/>
         <filter val="03-10-2026 12:55AM"/>
-        <filter val="03-10-2026 12:05AM"/>
-        <filter val="03-10-2026 04:15AM"/>
-        <filter val="03-09-2026 10:03PM"/>
-        <filter val="03-10-2026 05:56AM"/>
-        <filter val="03-10-2026 01:19AM"/>
-        <filter val="03-09-2026 09:40PM"/>
-        <filter val="03-09-2026 10:26PM"/>
-        <filter val="03-10-2026 06:55AM"/>
-        <filter val="03-09-2026 11:34PM"/>
-        <filter val="03-10-2026 01:26AM"/>
-        <filter val="03-09-2026 11:15PM"/>
-        <filter val="03-10-2026 04:29AM"/>
-        <filter val="03-10-2026 06:51AM"/>
-        <filter val="03-09-2026 09:17PM"/>
-        <filter val="03-09-2026 09:13PM"/>
-        <filter val="03-09-2026 09:36PM"/>
-        <filter val="03-09-2026 09:32PM"/>
-        <filter val="03-10-2026 01:07AM"/>
-        <filter val="03-09-2026 09:51PM"/>
-        <filter val="03-09-2026 10:55PM"/>
-        <filter val="03-10-2026 06:05AM"/>
-        <filter val="03-10-2026 04:14AM"/>
-        <filter val="03-09-2026 09:09PM"/>
-        <filter val="03-10-2026 06:20AM"/>
-        <filter val="03-10-2026 12:31AM"/>
-        <filter val="03-09-2026 11:26PM"/>
-        <filter val="03-09-2026 10:48PM"/>
-        <filter val="03-09-2026 10:25PM"/>
-        <filter val="03-09-2026 09:24PM"/>
-        <filter val="03-09-2026 09:43PM"/>
-        <filter val="03-09-2026 09:20PM"/>
-        <filter val="03-10-2026 08:19AM"/>
-        <filter val="03-09-2026 10:29PM"/>
-        <filter val="03-09-2026 09:39PM"/>
-        <filter val="03-09-2026 09:35PM"/>
-        <filter val="03-09-2026 09:58PM"/>
-        <filter val="03-09-2026 09:16PM"/>
-        <filter val="03-10-2026 03:21AM"/>
-        <filter val="03-09-2026 11:23PM"/>
-        <filter val="03-09-2026 10:24PM"/>
-        <filter val="03-09-2026 09:00PM"/>
-        <filter val="03-09-2026 10:01PM"/>
-        <filter val="03-09-2026 09:27PM"/>
-        <filter val="03-10-2026 02:37AM"/>
-        <filter val="03-09-2026 09:23PM"/>
-        <filter val="03-09-2026 11:13PM"/>
-        <filter val="03-09-2026 09:19PM"/>
-        <filter val="03-09-2026 11:32PM"/>
-        <filter val="03-09-2026 11:51PM"/>
-        <filter val="03-09-2026 09:15PM"/>
-        <filter val="03-09-2026 09:53PM"/>
-        <filter val="03-09-2026 09:11PM"/>
-        <filter val="03-09-2026 10:57PM"/>
-        <filter val="03-10-2026 07:31AM"/>
-        <filter val="03-09-2026 11:09PM"/>
-        <filter val="03-10-2026 06:41AM"/>
-        <filter val="03-09-2026 09:26PM"/>
-        <filter val="03-09-2026 09:45PM"/>
-        <filter val="03-09-2026 09:41PM"/>
-        <filter val="03-09-2026 10:27PM"/>
       </filters>
     </filterColumn>
     <filterColumn colId="12">
       <filters>
         <filter val="HANNAH"/>
+        <filter val="JENEATH LECIAS"/>
         <filter val="KATHLEEN DREW"/>
-        <filter val="JENEATH LECIAS"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <mergeCells count="39">
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="B148:B149"/>
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="B159:B160"/>
     <mergeCell ref="B111:B112"/>
@@ -10674,10 +10681,38 @@
     <mergeCell ref="B121:B122"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="B132:B133"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B21:B22"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>